--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>УБТ</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -458,39 +458,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Обследование объекта и разработка ТЗ</t>
+          <t>Проектно-изыскательные работы:
+Предпроектное обследование
+Разработка комплекта рабочей документации</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6545760</v>
+        <v>5398200</v>
       </c>
       <c r="C2" t="n">
-        <v>7011437.65</v>
+        <v>7413520.06</v>
       </c>
       <c r="D2" t="n">
-        <v>7717417.13</v>
+        <v>7385177.72</v>
       </c>
       <c r="E2" t="n">
-        <v>7091538.26</v>
+        <v>6732299.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Пусконаладочные работы:
+ПНР вновь смонтированного  полевого оборудования
+ПНР аппаратной части вновь вводимых каналов АСУТП
+Участие в комплексных испытаниях в части обеспечения работы вновь смонтированного полевого оборудования
+Устранение замечаний по результатам опытной эксплуатации</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3760642.76</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4737738.75</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3866127.17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>6545760</v>
-      </c>
-      <c r="C3" t="n">
-        <v>7011437.65</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7717417.13</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7091538.26</v>
+      <c r="B4" t="n">
+        <v>8498200</v>
+      </c>
+      <c r="C4" t="n">
+        <v>11174162.82</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12122916.47</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10598426.43</v>
       </c>
     </row>
   </sheetData>
